--- a/notebooks/new_abr/Shared model arrows.xlsx
+++ b/notebooks/new_abr/Shared model arrows.xlsx
@@ -724,7 +724,7 @@
     <t>beta</t>
   </si>
   <si>
-    <t>Per contact per unit time infection colonization probability</t>
+    <t>Per contact per unit time infection colonization probability (divide by population size for frequency dependence)</t>
   </si>
   <si>
     <t>CR_N</t>
@@ -10899,7 +10899,7 @@
         <v>228</v>
       </c>
       <c r="D7" s="8">
-        <v>1.0</v>
+        <v>0.25</v>
       </c>
       <c r="E7" s="9"/>
     </row>
@@ -11107,7 +11107,7 @@
         <v>257</v>
       </c>
       <c r="D24" s="5">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="25">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="8">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="26">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="C34" s="47"/>
       <c r="D34" s="46">
-        <v>0.5</v>
+        <v>2.0</v>
       </c>
       <c r="E34" s="48"/>
     </row>
